--- a/www/download/COUNTRY.WWW.WIOD16.xlsx
+++ b/www/download/COUNTRY.WWW.WIOD16.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>Mundo</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,1848 +852,3409 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>7.847</t>
+          <t>229.739420564356</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>7.883</t>
+          <t>275.96453071732</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>8.13</t>
+          <t>253.530480788097</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>9.075</t>
+          <t>234.898874727413</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>10.22</t>
+          <t>69225.393509955</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>11.179</t>
+          <t>105524.972060208</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>12.088</t>
+          <t>241.596404495011</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>13.542</t>
+          <t>239.980593819397</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>15.266</t>
+          <t>253.844758054548</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>15.267</t>
+          <t>274.895534550612</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>16.766</t>
+          <t>244.069842308745</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>18.68</t>
+          <t>235.145050032536</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>19.178</t>
+          <t>250.469506990681</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>19.561</t>
+          <t>273.242665325135</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>20.002</t>
+          <t>306.190351579617</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>2880.537</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2932.349</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>2983.112</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>3042.556</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>3109.826</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>3156.019</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>3202.181</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>3250.085</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>3288.898</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>3306.051</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>3338.984</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>3472.798</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>3649.263</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>3813.588</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>3954.229</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>1490.31</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1519.61</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>1545.867</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>1576.687</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>1618.442</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>1658.923</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>1703.912</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>1749.108</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>1783.849</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>1795.767</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>1820.797</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>1893.274</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>1987.338</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>2079.439</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>2161.813</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>5435359.568</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>5620187.688</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>5803771.87</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>5968603.951</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>6154539.871</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>6193953.057</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>6244516.084</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>6353907.563</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>6479929.161</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>6517642.265</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>6607148.458</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>6929248.423</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>7313026.542</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>7687668.269</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>7992262.151</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2809079.006</t>
+          <t>7658701411332.19</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2892064.697</t>
+          <t>7653746850571.07</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2973936.356</t>
+          <t>7865084820221.58</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>3054582.497</t>
+          <t>8167820014677.31</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>3160246.766</t>
+          <t>8424474937217.13</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>3215876.111</t>
+          <t>8667252287930.69</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>3287171.254</t>
+          <t>9007113120862.78</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>3384123.972</t>
+          <t>9114223855183.56</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>3469604.887</t>
+          <t>9372974072963.83</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>3494833.016</t>
+          <t>9523443858599.99</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>3558445.83</t>
+          <t>9539870767126.89</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>3728988.968</t>
+          <t>10156949520857.8</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>3930840.896</t>
+          <t>10697898472633.5</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>4138111.091</t>
+          <t>11094179741318.1</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>4315651.405</t>
+          <t>11354351157171.2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2084863820621.48</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2101880171784.76</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2181979998502.07</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2208300955080.61</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2209576968060.04</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2229753162592.01</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2265171382121.82</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2204222937125.17</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2242636188408.45</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>2267176826425.66</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>2223565892885.32</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>2282072349236.77</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>2388132108917.47</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>2435099776162.26</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2480147168831.98</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>250104856.804533</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>242303294.206304</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>226106643.630329</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>198775582.8274</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>174243357.692179</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>153963481.813936</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>135835914.806612</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>111902867.510114</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>99560830.5365557</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>105737020.108591</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>92811122.2087574</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>85011941.856457</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>88669911.4057298</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>88083004.1072635</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>89325181.6666303</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>32661827.2967165</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>32845073.8416418</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>33991212.0334108</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>37548985.5301068</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>42316660.2635565</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>45648176.5922173</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>49147848.8324442</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>56218294.4290552</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>62038743.2480645</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>56605754.4836621</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>63078236.4344416</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>69671439.7597008</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>71429420.5306162</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>74434535.2953624</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>77077315.067112</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>62229753.3193865</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>61604960.2125258</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>63685981.2160894</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>71977032.6483746</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>82076833.9959776</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>90663628.2520401</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>99535949.1494321</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>113719038.465387</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>126934817.736997</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>117369540.767418</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>130255885.319046</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>147274986.659704</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>151139918.668272</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>156582791.006788</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>160997197.961565</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>0.347368100632875</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0.375941757313781</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0.362953078415819</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0.383227449005872</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0.430249686523956</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>0.442256553234493</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0.451179932547898</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0.53529115197188</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>0.547110005938695</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>0.541491150947524</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>0.60033297943096</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>0.634036260583436</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>0.645989717921544</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>0.699359973260164</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0.740078758070218</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>7846223.87592984</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>7875336.47864516</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>8113298.99872537</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>9060000.30607258</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>10212240.6885657</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>11175012.1341031</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>12090068.6793164</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>13521864.4472986</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>15256973.3726471</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>15273124.0971955</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>16757131.4064602</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>18656026.4633716</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>19163619.8626624</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>19561546.4027473</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>20001321.5491715</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>229.739420564356</t>
+          <t>1398.94611268908</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>275.96453071732</t>
+          <t>1383.1706742938</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>253.530480788097</t>
+          <t>1411.49247380119</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>234.898874727413</t>
+          <t>1400.59574664761</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>69225.393509955</t>
+          <t>1365.24923021257</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>105524.972060208</t>
+          <t>1344.09722354325</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>241.596404495011</t>
+          <t>1329.39476564705</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>239.980593819397</t>
+          <t>1260.19839656336</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>253.844758054548</t>
+          <t>1257.18934838711</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>274.895534550612</t>
+          <t>1262.51190924584</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>244.069842308745</t>
+          <t>1221.20471151877</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>235.145050032536</t>
+          <t>1205.35755906791</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>250.469506990681</t>
+          <t>1201.67402609172</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>273.242665325135</t>
+          <t>1171.03665809102</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>306.190351579617</t>
+          <t>1147.25319183366</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>16.707</t>
+          <t>-7.21216201782227e-06</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>16.614</t>
+          <t>-6.58631324768066e-06</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>17.113</t>
+          <t>-1.99675559997559e-06</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>19.044</t>
+          <t>2.33948230743408e-05</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>21.132</t>
+          <t>4.63724136352539e-05</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>22.635</t>
+          <t>4.4703483581543e-06</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>24.438</t>
+          <t>7.15255737304688e-07</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>27.329</t>
+          <t>2.6702880859375e-05</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>30.23</t>
+          <t>3.39746475219727e-05</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>29.119</t>
+          <t>-2.68816947937012e-05</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>31.253</t>
+          <t>-1.20997428894043e-05</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>34.72</t>
+          <t>-6.28829002380371e-06</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>35.746</t>
+          <t>2.78949737548828e-05</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>36.663</t>
+          <t>5.40018081665039e-05</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>37.697</t>
+          <t>-1.35898590087891e-05</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>19.07</t>
+          <t>-1.18613243103027e-05</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>18.929</t>
+          <t>-2.80141830444336e-06</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>19.525</t>
+          <t>-1.4573335647583e-05</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>21.751</t>
+          <t>1.82688236236572e-05</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>24.133</t>
+          <t>2.14278697967529e-05</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>25.863</t>
+          <t>3.80277633666992e-05</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>27.869</t>
+          <t>1.4185905456543e-05</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>31.105</t>
+          <t>2.98023223876953e-07</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>34.391</t>
+          <t>3.39746475219727e-06</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>33.077</t>
+          <t>2.24411487579346e-05</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>35.582</t>
+          <t>-1.54972076416016e-05</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>39.468</t>
+          <t>2.03251838684082e-05</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>40.562</t>
+          <t>1.50501728057861e-05</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>41.498</t>
+          <t>3.84151935577393e-05</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>42.541</t>
+          <t>2.9832124710083e-05</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>90.724</t>
+          <t>2.03214585781097e-06</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>91.771</t>
+          <t>2.08429992198944e-06</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>96.862</t>
+          <t>2.97278165817261e-06</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>109.641</t>
+          <t>3.1106173992157e-06</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>124.556</t>
+          <t>-1.38580799102783e-06</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>136.327</t>
+          <t>-8.13230872154236e-06</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>147.764</t>
+          <t>-3.24100255966187e-06</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>165.294</t>
+          <t>-3.74391674995422e-06</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>184.522</t>
+          <t>4.34741377830505e-06</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>182.203</t>
+          <t>4.41074371337891e-06</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>195.269</t>
+          <t>8.94069671630859e-07</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>217.383</t>
+          <t>-1.81794166564941e-06</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>223.974</t>
+          <t>5.78910112380981e-06</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>231.217</t>
+          <t>1.4379620552063e-06</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>238.116</t>
+          <t>2.35438346862793e-06</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>62.23</t>
+          <t>1884.89536674163</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>61.605</t>
+          <t>1903.1622882527</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>63.686</t>
+          <t>1923.79801232809</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>71.977</t>
+          <t>1937.34248172384</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>82.077</t>
+          <t>1952.6472835386</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>90.664</t>
+          <t>1938.53302883954</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>99.536</t>
+          <t>1929.19100634122</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>113.719</t>
+          <t>1934.77144797287</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>126.935</t>
+          <t>1945.01022024925</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>117.37</t>
+          <t>1946.15093606832</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>130.256</t>
+          <t>1954.33417447996</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>147.275</t>
+          <t>1969.59795848531</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>151.14</t>
+          <t>1977.94309124036</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>156.583</t>
+          <t>1990.01282398022</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>160.997</t>
+          <t>1996.31090923801</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>31.645</t>
+          <t>1886.92568677945</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>31.479</t>
+          <t>1916.6162541256</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>32.776</t>
+          <t>1945.54265542718</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>36.712</t>
+          <t>1961.70687863917</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>41.251</t>
+          <t>1979.06241835042</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>44.678</t>
+          <t>1962.58436009592</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>48.345</t>
+          <t>1950.08224661753</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>54.427</t>
+          <t>1954.99752587698</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>59.892</t>
+          <t>1970.24305937797</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>56.885</t>
+          <t>1971.42827717617</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>62.055</t>
+          <t>1978.79009024089</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>68.812</t>
+          <t>1995.29263677865</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>70.263</t>
+          <t>2003.97353373256</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>72.106</t>
+          <t>2015.86248510534</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>73.807</t>
+          <t>2021.19334237083</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>7118189.71789185</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>6893203.93872495</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>7218844.07597103</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>8390644.25217276</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>10165692.7742245</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>11504494.9028253</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>13237538.412522</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>15511500.6914944</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>17650537.0137077</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>14040233.6855945</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>16761197.8883159</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>19795237.7095888</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>19834314.8469027</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>20299607.5491693</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>20648562.6814829</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>887053283516.182</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>887122927604.88</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>932999536493.893</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>1023302284082.74</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>1128602621289.53</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>1171606477925.83</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>1227287018965.14</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>1216277449533.14</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>1219581615037.1</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>1065465435949.34</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>1143943971638.99</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>1296540772107.01</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>1305617049669.63</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>1337400725220.72</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>1339176408890.45</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>7118189.71789185</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>6893203.93872495</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>7218844.07597103</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>8390644.25217276</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>10165692.7742245</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>11504494.9028253</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>13237538.412522</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>15511500.6914944</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>17650537.0137077</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>14040233.6855945</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>16761197.8883159</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>19795237.7095888</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>19834314.8469027</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>20299607.5491693</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>20648562.6814829</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>5435359.568</t>
+          <t>887053283516.182</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>5620187.688</t>
+          <t>887122927604.88</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>5803771.87</t>
+          <t>932999536493.893</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>5968603.951</t>
+          <t>1023302284082.74</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>6154539.871</t>
+          <t>1128602621289.53</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>6193953.057</t>
+          <t>1171606477925.83</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>6244516.084</t>
+          <t>1227287018965.14</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>6353907.563</t>
+          <t>1216277449533.14</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>6479929.161</t>
+          <t>1219581615037.1</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>6517642.265</t>
+          <t>1065465435949.34</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>6607148.458</t>
+          <t>1143943971638.99</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>6929248.423</t>
+          <t>1296540772107.01</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>7313026.542</t>
+          <t>1305617049669.63</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>7687668.269</t>
+          <t>1337400725220.72</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>7992262.151</t>
+          <t>1339176408890.45</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2809079.006</t>
+          <t>-5.32054400537163e-11</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2892064.697</t>
+          <t>-1.65982783073559e-11</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2973936.356</t>
+          <t>2.8421709430404e-11</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>3054582.497</t>
+          <t>-2.97291080642026e-11</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>3160246.766</t>
+          <t>-1.88720150617883e-11</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>3215876.111</t>
+          <t>1.50862433656584e-10</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>3287171.254</t>
+          <t>-7.13384906703141e-11</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>3384123.972</t>
+          <t>3.08091330225579e-10</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>3469604.887</t>
+          <t>-4.92264007334597e-11</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>3494833.016</t>
+          <t>4.78621586808003e-11</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>3558445.83</t>
+          <t>1.26192389870994e-10</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>3728988.968</t>
+          <t>-3.12638803734444e-11</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>3930840.896</t>
+          <t>-2.44313014263753e-10</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>4138111.091</t>
+          <t>-2.14981810131576e-10</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>4315651.405</t>
+          <t>-2.72848410531878e-11</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>7658947.361</t>
+          <t>-2.9146671295166e-05</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>7654874.728</t>
+          <t>2.86102294921875e-05</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>7866338.425</t>
+          <t>7.54296779632568e-05</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>8168590.894</t>
+          <t>-1.10268592834473e-06</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>8425170.968</t>
+          <t>-3.25441360473633e-05</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>8667951.658</t>
+          <t>4.88758087158203e-05</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>9007104.07</t>
+          <t>-1.60932540893555e-05</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>9115315.465</t>
+          <t>-4.11570072174072e-05</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>9373798.993</t>
+          <t>5.88297843933105e-05</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>9523696.172</t>
+          <t>-1.26957893371582e-05</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>9540839.098</t>
+          <t>8.8810920715332e-06</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>10158770.256</t>
+          <t>-6.22868537902832e-06</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>10698797.383</t>
+          <t>1.96397304534912e-05</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>11094375.661</t>
+          <t>-2.71499156951904e-05</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>11354272.667</t>
+          <t>-1.12056732177734e-05</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>62.23</t>
+          <t>13832773.6580954</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>61.605</t>
+          <t>13508644.467527</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>63.686</t>
+          <t>13985825.7069609</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>71.977</t>
+          <t>15787524.5883656</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>82.077</t>
+          <t>18020980.2868461</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>90.664</t>
+          <t>19657676.070124</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>99.536</t>
+          <t>21496962.1323555</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>113.719</t>
+          <t>24341030.8657769</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>126.935</t>
+          <t>27198886.1505307</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>117.37</t>
+          <t>25191999.5918471</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>130.256</t>
+          <t>28203627.0880657</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>147.275</t>
+          <t>31865048.1339443</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>151.14</t>
+          <t>32521091.3141858</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>156.583</t>
+          <t>33375562.6070077</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>160.997</t>
+          <t>34016180.5369134</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>4019736.05</t>
+          <t>0.0390253169531599</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>4080643.5</t>
+          <t>0.0380207135304752</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>4197843.241</t>
+          <t>0.0409281752423121</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>4260989.155</t>
+          <t>0.0417662574503293</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>4343438.05</t>
+          <t>0.042669550572469</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>4363869.731</t>
+          <t>0.041994557274931</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>4447440.727</t>
+          <t>0.0415001726495839</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>4505719.773</t>
+          <t>0.0429055975186586</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>4580993.161</t>
+          <t>0.0381204905772786</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>4593029.174</t>
+          <t>0.0306829776865268</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>4619816.005</t>
+          <t>0.0317494855072784</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>4804952.373</t>
+          <t>0.0305438576221772</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>5055876.009</t>
+          <t>0.0278169782819499</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>5273824.206</t>
+          <t>0.0284448270713169</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>5435889.025</t>
+          <t>0.0282918233069727</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>32.661</t>
+          <t>16707186.0164064</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>32.84</t>
+          <t>16613738.5067708</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>33.986</t>
+          <t>17112591.9583954</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>37.545</t>
+          <t>19044350.1314139</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>42.313</t>
+          <t>21131723.9038133</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>45.644</t>
+          <t>22634969.1273193</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>49.148</t>
+          <t>24438270.7506687</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>56.212</t>
+          <t>27328567.7543659</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>62.033</t>
+          <t>30229509.1438691</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>56.604</t>
+          <t>29118596.9345214</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>63.072</t>
+          <t>31252637.9623551</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>69.659</t>
+          <t>34720423.9905335</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>71.423</t>
+          <t>35746329.5963763</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>74.433</t>
+          <t>36662916.8074205</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>77.078</t>
+          <t>37696666.8173697</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2084936.279</t>
+          <t>19070413.6996621</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2102073.868</t>
+          <t>18928549.6680496</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2182191.487</t>
+          <t>19524790.2509453</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2208467.068</t>
+          <t>21751377.0438138</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2209677.18</t>
+          <t>24133290.910503</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2229823.532</t>
+          <t>25862970.8257554</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2265198.756</t>
+          <t>27868718.708084</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>2204421.855</t>
+          <t>31104617.4993084</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2242645.991</t>
+          <t>34391272.0989663</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2267177.05</t>
+          <t>33077161.0130693</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2223712.328</t>
+          <t>35581769.4747042</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>2282378.811</t>
+          <t>39467876.5738791</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>2388280.219</t>
+          <t>40561562.0428979</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>2435136.303</t>
+          <t>41497945.4177504</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2480107.988</t>
+          <t>42541022.6510366</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>34.73</t>
+          <t>90723840.6694089</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>37.58</t>
+          <t>91771183.0822633</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>36.28</t>
+          <t>96862432.2529047</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>38.31</t>
+          <t>109641205.323408</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>43.02</t>
+          <t>124556428.815013</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>44.22</t>
+          <t>136327343.725308</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>45.12</t>
+          <t>147763940.548064</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>53.52</t>
+          <t>165294229.808337</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>54.71</t>
+          <t>184522328.27655</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>54.15</t>
+          <t>182203128.545811</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>60.02</t>
+          <t>195269241.917272</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>63.38</t>
+          <t>217382827.584967</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>64.59</t>
+          <t>223974131.252149</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>69.93</t>
+          <t>231217016.365275</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>74.01</t>
+          <t>238115877.478904</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>250.12</t>
+          <t>22872783.6337651</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>242.348</t>
+          <t>23145209.7218311</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>226.143</t>
+          <t>23347647.2890653</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>198.788</t>
+          <t>23718480.4645377</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>174.253</t>
+          <t>24253266.0556216</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>153.973</t>
+          <t>24910584.8540942</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>135.843</t>
+          <t>25817322.8064179</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>111.925</t>
+          <t>26530241.5697092</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>99.572</t>
+          <t>27091441.3074486</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>105.742</t>
+          <t>26505070.1107914</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>92.824</t>
+          <t>27217098.9068875</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>85.032</t>
+          <t>28105969.9138871</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>88.678</t>
+          <t>28938602.8927759</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>88.083</t>
+          <t>29424176.7311881</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>89.322</t>
+          <t>30180550.5489019</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>19938457.361538</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>20173544.3165317</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>20321311.0709178</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>20631213.8312892</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>21125093.4478587</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>21704108.7564283</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>22531807.3504407</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>23231053.1879984</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>23681667.4786766</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>23080053.8072034</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>23704297.8542859</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>24538782.0274538</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>25260580.3568708</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>25713569.5958703</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>26417178.166213</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>11386750.5132615</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>11364542.3409687</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>12077701.6003688</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>13639303.1147745</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>15527007.527014</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>16900018.5783148</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>18222297.7234439</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>20613912.1436117</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>22291055.0490108</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>20863658.624782</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>22956829.3727299</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>25295736.5986332</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>25393903.407422</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>26138474.4492034</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>26738053.8813894</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>2809079006068.96</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2892064697228.51</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>2973936356000.14</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>3054582496733.38</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>3160246765918.43</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>3215876110843.66</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>3287171253516.98</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>3384123972341.74</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>3469604886766.92</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>3494833015568.45</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>3558445830322.22</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>3728988967927.7</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>3930840896316.45</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>4138111090504.92</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>4315651405372.53</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>5435359567899.25</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>5620187687870.89</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>5803771870469.88</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>5968603951483.1</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>6154539871462.13</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>6193953057225.88</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>6244516084436.31</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>6353907562550.06</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>6479929160659.97</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>6517642265291.28</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>6607148458378.88</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>6929248423114.86</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>7313026541991.18</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>7687668269104.19</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>7992262151012.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>4019736050217.03</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>4080643500214.89</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>4197843240850.81</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>4260989155275.51</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>4343438050187.65</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>4363869730746.82</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>4447440727332.58</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>4505719773026.27</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>4580993161294.67</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>4593029174128.79</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>4619816005464.27</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>4804952373344.11</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>5055876008989.74</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>5273824206470.04</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>5435889025427.87</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>2880537164.7551</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2932348964.3653</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>2983112117.4753</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>3042556467.7754</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>3109826054.1939</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>3156018759.3277</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>3202180879.9437</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>3250084707.7542</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>3288898356.8889</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>3306050917.8792</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>3338984003.8943</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>3472798072.5183</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>3649263036.1091</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>3813587645.9363</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>3954229406.6916</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>1490310314.10775</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1519610132.6092</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>1545867256.8235</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>1576686892.25016</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>1618442200.26845</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>1658922526.9836</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>1703911765.45614</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>1749107873.12238</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>1783849180.14585</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>1795766685.30594</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>1820797014.54799</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>1893274184.13625</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>1987337711.44621</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>2079439408.9523</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>2161813265.35945</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>5435359567899.25</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>5620187687870.89</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>5803771870469.88</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>5968603951483.1</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>6154539871462.13</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>6193953057225.88</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>6244516084436.31</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>6353907562550.06</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>6479929160659.97</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>6517642265291.28</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>6607148458378.88</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>6929248423114.86</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>7313026541991.18</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>7687668269104.19</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>7992262151012.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>2809079006068.96</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2892064697228.51</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>2973936356000.14</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>3054582496733.38</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>3160246765918.43</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>3215876110843.66</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>3287171253516.98</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>3384123972341.74</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>3469604886766.92</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>3494833015568.45</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>3558445830322.22</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>3728988967927.7</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>3930840896316.45</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>4138111090504.92</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>4315651405372.53</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>62229753.3193865</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>61604960.2125258</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>63685981.2160894</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>71977032.6483746</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>82076833.9959776</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>90663628.2520401</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>99535949.1494322</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>113719038.465387</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>126934817.736997</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>117369540.767418</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>130255885.319046</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>147274986.659704</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>151139918.668272</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>156582791.006788</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>160997197.961565</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>31644539.2110633</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>31479455.7128878</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>32775645.9863482</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>36712161.167748</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>41251114.9209817</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>44677772.5653578</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>48344897.0666069</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>54426589.7731068</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>59891534.2789202</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>56884939.6962316</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>62054623.0228873</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>68812306.2629739</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>70262786.5881451</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>72105635.0325916</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>73806917.7970671</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>111543714.240945</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>114698864.382503</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>118340900.588277</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>121154390.496684</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>126474375.957178</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>131148386.518152</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>136194290.950038</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>139915905.752697</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>143398475.756273</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>146831296.730378</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>149235980.856687</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>153683480.793293</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>158747738.530098</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>163478025.374887</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>168989746.804522</t>
         </is>
       </c>
     </row>
@@ -2699,7 +4265,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2722,36 +4288,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -2763,331 +4344,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3124,6 +5069,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>WIOD16</t>
